--- a/data/trans_dic/P19C01-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19C01-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue una revisión o chequeo</t>
+          <t>Población cuyo motivo por su última visita al dentista fue una revisión o chequeo (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,01; 26,52</t>
+          <t>20,23; 26,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,71; 20,5</t>
+          <t>14,91; 20,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,44; 31,63</t>
+          <t>23,68; 31,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33,64; 41,74</t>
+          <t>33,22; 41,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,68; 25,16</t>
+          <t>19,62; 25,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,61; 25,85</t>
+          <t>20,75; 25,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,37; 37,71</t>
+          <t>29,67; 37,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>38,34; 44,11</t>
+          <t>38,42; 44,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,4; 24,86</t>
+          <t>20,93; 24,93</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,94; 22,72</t>
+          <t>18,9; 22,71</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,39; 34,34</t>
+          <t>28,5; 34,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37,28; 41,86</t>
+          <t>36,96; 41,96</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,13; 32,26</t>
+          <t>27,2; 32,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,23; 33,64</t>
+          <t>29,05; 33,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39,12; 43,82</t>
+          <t>39,33; 44,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36,27; 59,97</t>
+          <t>38,46; 59,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,77; 37,81</t>
+          <t>32,84; 38,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,42; 39,43</t>
+          <t>34,2; 39,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,84; 47,05</t>
+          <t>42,16; 46,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>43,74; 64,78</t>
+          <t>40,37; 64,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,79; 34,39</t>
+          <t>30,81; 34,45</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32,33; 35,73</t>
+          <t>32,48; 35,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41,25; 44,75</t>
+          <t>41,44; 44,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>44,45; 61,08</t>
+          <t>43,37; 60,84</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35,89; 44,96</t>
+          <t>35,67; 45,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37,9; 47,74</t>
+          <t>38,36; 48,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45,72; 54,67</t>
+          <t>45,73; 55,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>64,76; 72,8</t>
+          <t>65,06; 72,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34,38; 44,35</t>
+          <t>34,41; 44,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,47; 59,76</t>
+          <t>49,6; 59,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,26; 56,32</t>
+          <t>47,26; 56,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>64,05; 70,61</t>
+          <t>64,46; 70,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36,36; 43,06</t>
+          <t>36,55; 43,3</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45,28; 52,31</t>
+          <t>44,9; 52,25</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48,05; 54,48</t>
+          <t>47,93; 54,45</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>65,33; 70,61</t>
+          <t>65,54; 70,87</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,17; 31,6</t>
+          <t>27,99; 31,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27,77; 31,27</t>
+          <t>27,68; 31,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38,74; 42,58</t>
+          <t>38,68; 42,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40,66; 58,09</t>
+          <t>39,1; 58,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,68; 33,38</t>
+          <t>29,71; 33,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,58; 36,11</t>
+          <t>32,6; 36,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,58; 45,34</t>
+          <t>41,45; 45,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46,11; 60,09</t>
+          <t>43,56; 60,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,41; 31,95</t>
+          <t>29,36; 31,92</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30,78; 33,16</t>
+          <t>30,82; 33,19</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40,74; 43,53</t>
+          <t>40,84; 43,42</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>47,4; 58,45</t>
+          <t>47,86; 58,15</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue una revisión o chequeo</t>
+          <t>Población cuyo motivo por su última visita al dentista fue una revisión o chequeo (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>137967; 182834</t>
+          <t>139478; 183055</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>114583; 159724</t>
+          <t>116191; 156497</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>107215; 144699</t>
+          <t>108328; 145202</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>162959; 202222</t>
+          <t>160943; 201668</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>188763; 241256</t>
+          <t>188178; 240525</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>232499; 291643</t>
+          <t>234081; 291333</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>194057; 240928</t>
+          <t>189584; 242415</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>276692; 318299</t>
+          <t>277240; 317702</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>336201; 409817</t>
+          <t>344985; 410961</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>361260; 433400</t>
+          <t>360586; 433220</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>311288; 376512</t>
+          <t>312412; 376734</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>449581; 504873</t>
+          <t>445745; 506029</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>356551; 424081</t>
+          <t>357515; 423722</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>493464; 567900</t>
+          <t>490396; 570058</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>663724; 743423</t>
+          <t>667214; 748902</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>809027; 1337705</t>
+          <t>857760; 1334330</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>449688; 518810</t>
+          <t>450667; 522558</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>547037; 626605</t>
+          <t>543547; 625251</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>714942; 803975</t>
+          <t>720362; 801725</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>961360; 1423827</t>
+          <t>887290; 1414366</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>827123; 923958</t>
+          <t>827857; 925693</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1059526; 1171164</t>
+          <t>1064522; 1171170</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1404764; 1524022</t>
+          <t>1411232; 1521800</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1968663; 2704690</t>
+          <t>1920650; 2694421</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>162390; 203397</t>
+          <t>161404; 203994</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>167548; 211067</t>
+          <t>169609; 214395</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>228234; 272946</t>
+          <t>228325; 275015</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>409318; 460100</t>
+          <t>411209; 457038</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>140539; 181311</t>
+          <t>140654; 180364</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>209633; 253208</t>
+          <t>210148; 253337</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>240249; 286297</t>
+          <t>240228; 285744</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>417362; 460098</t>
+          <t>420018; 462002</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>313150; 370840</t>
+          <t>314785; 372892</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>392027; 452897</t>
+          <t>388743; 452391</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>484183; 548873</t>
+          <t>482891; 548577</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>838533; 906322</t>
+          <t>841283; 909713</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>692031; 776288</t>
+          <t>687407; 777003</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>808037; 909703</t>
+          <t>805411; 907108</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1027788; 1129720</t>
+          <t>1026277; 1126684</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1361013; 1944285</t>
+          <t>1308733; 1947985</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>813224; 914498</t>
+          <t>813931; 907265</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1023478; 1134161</t>
+          <t>1023924; 1133320</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1187554; 1294915</t>
+          <t>1183916; 1293182</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1646578; 2145808</t>
+          <t>1555447; 2143540</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1528215; 1660205</t>
+          <t>1525596; 1658507</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1862630; 2006694</t>
+          <t>1865070; 2008171</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2244466; 2397900</t>
+          <t>2249900; 2391987</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3279152; 4043381</t>
+          <t>3311067; 4022774</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C01-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19C01-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,85%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,23; 26,55</t>
+          <t>20,18; 26,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,91; 20,09</t>
+          <t>14,72; 20,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,68; 31,74</t>
+          <t>23,39; 31,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33,22; 41,63</t>
+          <t>33,12; 41,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,62; 25,08</t>
+          <t>19,79; 24,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,75; 25,82</t>
+          <t>20,65; 25,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,67; 37,94</t>
+          <t>30,06; 37,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>38,42; 44,03</t>
+          <t>39,36; 44,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,93; 24,93</t>
+          <t>20,81; 25,17</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,9; 22,71</t>
+          <t>18,97; 22,6</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,5; 34,36</t>
+          <t>28,61; 33,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,96; 41,96</t>
+          <t>37,38; 42,0</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>60,55%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,2; 32,24</t>
+          <t>26,98; 32,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,05; 33,77</t>
+          <t>29,13; 33,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39,33; 44,14</t>
+          <t>39,28; 44,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38,46; 59,82</t>
+          <t>55,32; 60,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,84; 38,08</t>
+          <t>32,94; 38,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,2; 39,34</t>
+          <t>34,46; 39,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,16; 46,92</t>
+          <t>42,07; 46,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>40,37; 64,35</t>
+          <t>60,85; 64,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,81; 34,45</t>
+          <t>30,78; 34,65</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32,48; 35,73</t>
+          <t>32,24; 35,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41,44; 44,69</t>
+          <t>41,18; 44,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>43,37; 60,84</t>
+          <t>58,97; 62,12</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>67,92%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35,67; 45,09</t>
+          <t>35,53; 45,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,36; 48,49</t>
+          <t>37,85; 48,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45,73; 55,09</t>
+          <t>45,66; 55,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>65,06; 72,31</t>
+          <t>64,55; 72,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34,41; 44,12</t>
+          <t>34,07; 43,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,6; 59,79</t>
+          <t>49,63; 59,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,26; 56,21</t>
+          <t>47,45; 56,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>64,46; 70,9</t>
+          <t>64,0; 70,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36,55; 43,3</t>
+          <t>36,48; 43,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44,9; 52,25</t>
+          <t>45,23; 52,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47,93; 54,45</t>
+          <t>48,04; 54,53</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>65,54; 70,87</t>
+          <t>65,54; 70,63</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>58,15%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,99; 31,63</t>
+          <t>27,98; 31,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27,68; 31,18</t>
+          <t>27,89; 31,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38,68; 42,46</t>
+          <t>38,94; 42,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39,1; 58,2</t>
+          <t>55,27; 58,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,71; 33,11</t>
+          <t>29,66; 33,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,6; 36,08</t>
+          <t>32,62; 35,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,45; 45,28</t>
+          <t>41,53; 45,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>43,56; 60,02</t>
+          <t>57,69; 60,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,36; 31,92</t>
+          <t>29,28; 31,96</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30,82; 33,19</t>
+          <t>30,69; 33,17</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40,84; 43,42</t>
+          <t>40,84; 43,54</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>47,86; 58,15</t>
+          <t>57,0; 59,32</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>180962</t>
+          <t>196823</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>296274</t>
+          <t>329892</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>477235</t>
+          <t>526715</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>139478; 183055</t>
+          <t>139134; 182302</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>116191; 156497</t>
+          <t>114705; 157522</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>108328; 145202</t>
+          <t>106984; 143077</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>160943; 201668</t>
+          <t>177966; 222169</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>188178; 240525</t>
+          <t>189792; 239323</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>234081; 291333</t>
+          <t>232920; 289094</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>189584; 242415</t>
+          <t>192019; 240425</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>277240; 317702</t>
+          <t>308809; 351415</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>344985; 410961</t>
+          <t>343062; 414915</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>360586; 433220</t>
+          <t>361788; 430979</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>312412; 376734</t>
+          <t>313682; 370652</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>445745; 506029</t>
+          <t>494166; 555231</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1170440</t>
+          <t>1253366</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1259033</t>
+          <t>1324501</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2429473</t>
+          <t>2577868</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>357515; 423722</t>
+          <t>354626; 423785</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>490396; 570058</t>
+          <t>491775; 568978</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>667214; 748902</t>
+          <t>666342; 748258</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>857760; 1334330</t>
+          <t>1187355; 1300267</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>450667; 522558</t>
+          <t>451968; 522823</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>543547; 625251</t>
+          <t>547713; 623967</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>720362; 801725</t>
+          <t>718867; 801303</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>887290; 1414366</t>
+          <t>1284244; 1366564</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>827857; 925693</t>
+          <t>827020; 931053</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1064522; 1171170</t>
+          <t>1056842; 1168176</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1411232; 1521800</t>
+          <t>1402281; 1523107</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1920650; 2694421</t>
+          <t>2510530; 2644501</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>434804</t>
+          <t>482798</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>439713</t>
+          <t>486508</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>874518</t>
+          <t>969306</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>161404; 203994</t>
+          <t>160750; 203772</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>169609; 214395</t>
+          <t>167362; 212452</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>228325; 275015</t>
+          <t>227968; 276020</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>411209; 457038</t>
+          <t>453635; 509282</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>140654; 180364</t>
+          <t>139259; 178191</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>210148; 253337</t>
+          <t>210285; 252123</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>240228; 285744</t>
+          <t>241185; 287295</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>420018; 462002</t>
+          <t>463650; 512653</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>314785; 372892</t>
+          <t>314199; 375727</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>388743; 452391</t>
+          <t>391616; 454525</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>482891; 548577</t>
+          <t>484042; 549393</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>841283; 909713</t>
+          <t>935370; 1008103</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1786205</t>
+          <t>1932988</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1995020</t>
+          <t>2140900</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3781225</t>
+          <t>4073888</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>687407; 777003</t>
+          <t>687219; 780082</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>805411; 907108</t>
+          <t>811625; 912132</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1026277; 1126684</t>
+          <t>1033083; 1136496</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1308733; 1947985</t>
+          <t>1871676; 1995317</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>813931; 907265</t>
+          <t>812786; 908419</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1023924; 1133320</t>
+          <t>1024573; 1127810</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1183916; 1293182</t>
+          <t>1186049; 1290855</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1555447; 2143540</t>
+          <t>2087989; 2193378</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1525596; 1658507</t>
+          <t>1521653; 1660640</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1865070; 2008171</t>
+          <t>1857134; 2006864</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2249900; 2391987</t>
+          <t>2250137; 2398730</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3311067; 4022774</t>
+          <t>3993304; 4155888</t>
         </is>
       </c>
     </row>
